--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -466,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -493,12 +493,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -520,83 +520,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1625000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>196434.45</t>
+          <t>1625000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>184384</t>
+          <t>196434.45</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>196432</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>12050.45</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2.45</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -481,7 +496,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -493,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -508,7 +523,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -520,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -547,83 +562,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1625000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>196434.45</t>
+          <t>1744000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>196432</t>
+          <t>210434.45</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>196432</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2.45</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14002.45</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -562,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -589,83 +589,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1744000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>210434.45</t>
+          <t>1744000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>196432</t>
+          <t>210434.45</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>210432</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>14002.45</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2.45</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -550,7 +565,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -562,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -577,7 +592,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -589,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -616,83 +631,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1744000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>210434.45</t>
+          <t>1844000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>210432</t>
+          <t>222482.64</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>210432</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2.45</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12050.64</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -496,12 +496,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -604,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -658,83 +658,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1844000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>222482.64</t>
+          <t>1844000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>210432</t>
+          <t>222482.64</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>222480</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>12050.64</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2.64</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -619,7 +634,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -631,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -646,7 +661,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -658,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -685,83 +700,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1844000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>222482.64</t>
+          <t>1954000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>222480</t>
+          <t>235423.82</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>222480</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2.64</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>12943.82</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -538,12 +538,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -565,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -592,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -619,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -673,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -700,12 +700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -727,83 +727,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1954000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>235423.82</t>
+          <t>1954000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>222480</t>
+          <t>235423.82</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>222768</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>12943.82</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>12655.82</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -538,12 +538,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -565,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -592,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -619,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -673,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -700,12 +700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -727,12 +727,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -754,83 +754,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1954000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>235423.82</t>
+          <t>1954000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>222768</t>
+          <t>235423.82</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>235421</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>12655.82</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2.82</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,166 +411,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -580,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -592,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -607,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -619,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -673,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -715,7 +730,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -727,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -742,7 +757,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -754,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -781,83 +796,110 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1954000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>235423.82</t>
+          <t>2054000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>235421</t>
+          <t>247188.52</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>235421</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2.82</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>11767.52</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -796,12 +796,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -823,83 +823,110 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2054000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>247188.52</t>
+          <t>2054000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>235421</t>
+          <t>247188.52</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>235809</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>11767.52</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>11379.52</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -796,12 +796,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -823,12 +823,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -850,83 +850,110 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2054000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>247188.52</t>
+          <t>2054000</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>235809</t>
+          <t>247188.52</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>240809</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>11379.52</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6379.52</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -796,12 +796,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -823,12 +823,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -850,12 +850,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -877,83 +877,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2054000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>247188.52</t>
+          <t>2054000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>240809</t>
+          <t>247188.52</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>247185</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>6379.52</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3.52</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,166 +453,181 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +718,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -730,7 +745,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -742,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -796,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -823,12 +838,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -838,7 +853,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -850,12 +865,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -865,7 +880,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -877,12 +892,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -904,83 +919,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2054000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>247188.52</t>
+          <t>2154000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>247185</t>
+          <t>259093.28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>247185</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>3.52</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>11908.28</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,166 +495,181 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -745,7 +760,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -757,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -772,7 +787,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -784,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -811,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -838,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -865,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -880,7 +895,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -892,12 +907,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -907,7 +922,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -919,12 +934,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -946,83 +961,110 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2154000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>259093.28</t>
+          <t>2264000</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>247185</t>
+          <t>272188.52</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>247185</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>11908.28</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>25003.52</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,166 +537,181 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -718,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -745,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -787,7 +802,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -799,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -814,7 +829,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -826,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -853,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -880,12 +895,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -907,12 +922,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -922,7 +937,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -934,12 +949,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -949,7 +964,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -961,12 +976,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -988,83 +1003,110 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2264000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>272188.52</t>
+          <t>2434000</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>247185</t>
+          <t>292670.45</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>247185</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>25003.52</t>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>45485.45</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -706,12 +706,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -733,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -760,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -787,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -814,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -868,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -922,12 +922,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -949,12 +949,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -976,12 +976,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1030,83 +1030,110 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2434000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>292670.45</t>
+          <t>2434000</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>247185</t>
+          <t>292670.45</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>280762</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>45485.45</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>11908.45</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,166 +579,181 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -760,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -787,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -814,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -841,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -856,7 +871,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -868,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -883,7 +898,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -895,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -922,12 +937,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -949,12 +964,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -976,12 +991,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -991,7 +1006,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1003,12 +1018,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1018,7 +1033,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1030,12 +1045,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1057,83 +1072,110 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2434000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>292670.45</t>
+          <t>2544000</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>280762</t>
+          <t>305611.63</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>280762</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>11908.45</t>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>24849.63</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -748,12 +748,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -775,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -802,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -829,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -856,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -883,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -910,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -937,12 +937,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -964,12 +964,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -991,12 +991,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1018,12 +1018,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1045,12 +1045,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1072,12 +1072,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1099,83 +1099,110 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2544000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>305611.63</t>
+          <t>2544000</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>280762</t>
+          <t>305611.63</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>293703</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>24849.63</t>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>11908.63</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,166 +621,181 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -802,12 +817,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -829,12 +844,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -856,12 +871,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -883,12 +898,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -910,12 +925,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -925,7 +940,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -937,12 +952,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -952,7 +967,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -964,12 +979,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -991,12 +1006,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1018,12 +1033,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1045,12 +1060,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1060,7 +1075,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1072,12 +1087,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1087,7 +1102,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1099,12 +1114,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1126,83 +1141,110 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2544000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>305611.63</t>
+          <t>2704000</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>293703</t>
+          <t>324659.24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>293703</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>11908.63</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>30956.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -790,12 +790,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -817,12 +817,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -844,12 +844,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -898,12 +898,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -925,12 +925,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -952,12 +952,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -979,12 +979,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1006,12 +1006,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1033,12 +1033,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1060,12 +1060,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1087,12 +1087,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1114,12 +1114,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1141,12 +1141,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1168,83 +1168,110 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2704000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>324659.24</t>
+          <t>2704000</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>293703</t>
+          <t>324659.24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>312750</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>30956.24</t>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>11909.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,166 +663,181 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -832,7 +847,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -844,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -871,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -898,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -925,12 +940,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -952,12 +967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -979,12 +994,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -994,7 +1009,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1006,12 +1021,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1021,7 +1036,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1033,12 +1048,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1060,12 +1075,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1087,12 +1102,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1114,12 +1129,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1129,7 +1144,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1141,12 +1156,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1156,7 +1171,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1168,12 +1183,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1195,83 +1210,110 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2704000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>324659.24</t>
+          <t>2964000</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>312750</t>
+          <t>356174.4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>312750</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>11909.24</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>43424.4</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -832,12 +832,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -886,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -913,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -940,12 +940,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -967,12 +967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -994,12 +994,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1048,12 +1048,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1075,12 +1075,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1102,12 +1102,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1129,12 +1129,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1156,12 +1156,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1183,12 +1183,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1210,12 +1210,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1237,83 +1237,110 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2964000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>356174.4</t>
+          <t>2964000</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>312750</t>
+          <t>356174.4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>344265</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>43424.4</t>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>11909.4</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,166 +705,181 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -874,7 +889,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -886,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -901,7 +916,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -913,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -928,7 +943,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -940,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -967,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -994,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1021,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1048,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1063,7 +1078,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1075,12 +1090,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1102,12 +1117,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1117,7 +1132,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1129,7 +1144,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1156,12 +1171,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1183,12 +1198,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1198,7 +1213,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1210,12 +1225,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1237,12 +1252,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1252,7 +1267,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1264,12 +1279,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/08 11:30:43</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1288,59 +1303,113 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2964000</t>
-        </is>
-      </c>
-    </row>
+          <t>07/08 11:30:43</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>356174.4</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>344265</t>
+          <t>3064000</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>368222.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>356313</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>11909.4</t>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>11909.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,166 +747,181 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -916,7 +931,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -928,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -955,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -970,7 +985,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -982,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1009,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1036,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1063,12 +1078,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1090,12 +1105,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1117,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1132,7 +1147,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1144,12 +1159,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1159,7 +1174,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1171,12 +1186,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1198,12 +1213,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1225,12 +1240,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1252,12 +1267,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1267,7 +1282,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1279,12 +1294,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1294,7 +1309,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1306,12 +1321,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1333,83 +1348,110 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>3064000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>368222.59</t>
+          <t>3194000</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>356313</t>
+          <t>383698.78</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>356313</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>11909.59</t>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>27385.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -916,12 +916,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -943,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -970,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1024,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1078,12 +1078,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1105,12 +1105,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1132,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1186,12 +1186,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1213,12 +1213,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1240,12 +1240,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1267,12 +1267,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1294,12 +1294,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1321,12 +1321,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1348,12 +1348,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1375,83 +1375,110 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3194000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>383698.78</t>
+          <t>3194000</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>356313</t>
+          <t>383698.78</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>371789</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>27385.78</t>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>11909.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,166 +789,181 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -970,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -985,7 +1000,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -997,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1024,12 +1039,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1039,7 +1054,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1051,12 +1066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1078,12 +1093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1105,12 +1120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1132,12 +1147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1159,12 +1174,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1186,12 +1201,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1201,7 +1216,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1213,12 +1228,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1228,7 +1243,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1240,12 +1255,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1267,12 +1282,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1294,12 +1309,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1321,12 +1336,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1336,7 +1351,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1348,12 +1363,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1363,7 +1378,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1375,12 +1390,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1402,83 +1417,110 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>3194000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>383698.78</t>
+          <t>3294000</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>371789</t>
+          <t>395326.69</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>371789</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>11909.78</t>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>23537.69</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,166 +831,181 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1012,12 +1027,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1039,12 +1054,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1054,7 +1069,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1066,12 +1081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1093,12 +1108,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1108,7 +1123,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1120,12 +1135,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1135,7 +1150,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1147,12 +1162,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1174,12 +1189,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1201,12 +1216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1228,12 +1243,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1243,7 +1258,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1255,12 +1270,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1282,12 +1297,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1309,12 +1324,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1324,7 +1339,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1336,12 +1351,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1363,12 +1378,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1378,7 +1393,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1390,12 +1405,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1417,12 +1432,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1444,12 +1459,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/08 11:30:43</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1459,7 +1474,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1468,59 +1483,140 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>07/13 15:24:33</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>81808</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>07/08 11:30:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3294000</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>395326.69</t>
-        </is>
-      </c>
-    </row>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>371789</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3374000</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>404738.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>392828</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>23537.69</t>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>11910.45</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,166 +873,181 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1042,7 +1057,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1054,12 +1069,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1069,7 +1084,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1081,12 +1096,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1108,12 +1123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1123,7 +1138,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1135,12 +1150,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1162,12 +1177,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1177,7 +1192,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1189,12 +1204,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1216,12 +1231,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1243,12 +1258,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1270,12 +1285,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1297,12 +1312,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1324,12 +1339,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1339,7 +1354,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1351,12 +1366,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1366,7 +1381,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1378,12 +1393,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1405,12 +1420,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1432,12 +1447,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1459,12 +1474,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1474,7 +1489,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1486,12 +1501,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1501,7 +1516,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1513,12 +1528,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1540,83 +1555,110 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>3374000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>404738.45</t>
+          <t>3474000</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>392828</t>
+          <t>416503.16</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>392828</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>11910.45</t>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>23675.16</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -1042,12 +1042,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1069,12 +1069,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1096,12 +1096,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1123,12 +1123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1150,12 +1150,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1177,12 +1177,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1204,12 +1204,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1231,12 +1231,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1258,12 +1258,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1285,12 +1285,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1312,12 +1312,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1339,12 +1339,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1420,12 +1420,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1447,12 +1447,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1474,12 +1474,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1528,12 +1528,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1555,12 +1555,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1582,83 +1582,110 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>3474000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>416503.16</t>
+          <t>3474000</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>392828</t>
+          <t>416503.16</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>404592</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>23675.16</t>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>11911.16</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,166 +915,181 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1084,7 +1099,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1096,12 +1111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1111,7 +1126,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1123,12 +1138,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1138,7 +1153,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1150,12 +1165,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1177,12 +1192,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1192,7 +1207,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1204,12 +1219,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1231,12 +1246,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1246,7 +1261,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1258,12 +1273,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1285,12 +1300,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1312,12 +1327,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1339,12 +1354,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1366,12 +1381,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1393,12 +1408,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1408,7 +1423,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1420,12 +1435,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1435,7 +1450,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1447,12 +1462,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1474,12 +1489,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1501,12 +1516,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1528,12 +1543,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1543,7 +1558,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1555,12 +1570,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1570,7 +1585,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1582,12 +1597,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1609,83 +1624,110 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>3474000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>416503.16</t>
+          <t>3664000</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>404592</t>
+          <t>439394.72</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>404592</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>11911.16</t>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>34802.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 11:12:45</t>
+          <t>10/15 12:50:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>16766.47</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,166 +957,181 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1126,7 +1141,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1138,12 +1153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1153,7 +1168,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1165,12 +1180,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1180,7 +1195,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1192,12 +1207,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1219,12 +1234,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1234,7 +1249,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1246,12 +1261,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1273,12 +1288,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1288,7 +1303,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1300,12 +1315,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1327,12 +1342,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1354,12 +1369,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1381,12 +1396,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1408,12 +1423,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1435,12 +1450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1450,7 +1465,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1462,12 +1477,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1477,7 +1492,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1489,12 +1504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1516,12 +1531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1543,12 +1558,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1570,12 +1585,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1585,7 +1600,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1597,12 +1612,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1612,7 +1627,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1624,12 +1639,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1651,83 +1666,110 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>3664000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>439394.72</t>
+          <t>3804000</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>404592</t>
+          <t>456161.19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>404592</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>34802.72</t>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>51569.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 12:50:42</t>
+          <t>10/15 12:53:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16766.47</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/15 11:12:45</t>
+          <t>10/15 12:50:42</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>16766.47</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,166 +999,181 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1168,7 +1183,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1180,12 +1195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1195,7 +1210,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1207,12 +1222,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1222,7 +1237,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1234,12 +1249,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1261,12 +1276,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1276,7 +1291,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1288,12 +1303,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1315,12 +1330,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1330,7 +1345,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1342,12 +1357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1369,12 +1384,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1396,12 +1411,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1423,12 +1438,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1450,12 +1465,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1477,12 +1492,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1492,7 +1507,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1504,12 +1519,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1519,7 +1534,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1531,12 +1546,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1558,12 +1573,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1585,12 +1600,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1612,12 +1627,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1627,7 +1642,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1639,12 +1654,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1654,7 +1669,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1666,12 +1681,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1693,83 +1708,110 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>3804000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>456161.19</t>
+          <t>3904000</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>404592</t>
+          <t>468065.95</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>404592</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>51569.19</t>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>63473.95</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -1168,12 +1168,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1222,12 +1222,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1249,12 +1249,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1276,12 +1276,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1303,12 +1303,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1357,12 +1357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1384,12 +1384,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1411,12 +1411,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1438,12 +1438,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1465,12 +1465,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1492,12 +1492,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1546,12 +1546,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1573,12 +1573,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1600,12 +1600,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1708,12 +1708,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1735,83 +1735,110 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>3904000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>468065.95</t>
+          <t>3904000</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>404592</t>
+          <t>468065.95</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>456154</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>63473.95</t>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>11911.95</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 12:53:40</t>
+          <t>10/16 12:34:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/15 12:50:42</t>
+          <t>10/15 12:53:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16766.47</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/15 11:12:45</t>
+          <t>10/15 12:50:42</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>16766.47</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,7 +957,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,166 +1041,181 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1222,12 +1237,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1249,12 +1264,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1276,12 +1291,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1303,12 +1318,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1318,7 +1333,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1330,12 +1345,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1345,7 +1360,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1357,12 +1372,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1372,7 +1387,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1384,12 +1399,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1399,7 +1414,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1411,12 +1426,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1426,7 +1441,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1438,12 +1453,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1465,12 +1480,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1492,12 +1507,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1519,12 +1534,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1546,12 +1561,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1561,7 +1576,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1573,12 +1588,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1600,12 +1615,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1615,7 +1630,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1627,7 +1642,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1654,12 +1669,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1681,12 +1696,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1696,7 +1711,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1708,12 +1723,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1735,12 +1750,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1750,7 +1765,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1762,12 +1777,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/08 11:30:43</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1786,59 +1801,113 @@
         </is>
       </c>
     </row>
-    <row r="58"/>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>3904000</t>
-        </is>
-      </c>
-    </row>
+          <t>07/08 11:30:43</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>468065.95</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>456154</t>
+          <t>4204000</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>504651.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>492739</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>11911.95</t>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>11912.32</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/16 12:34:20</t>
+          <t>10/18 16:50:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>10465.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/15 12:53:40</t>
+          <t>10/16 12:34:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/15 12:50:42</t>
+          <t>10/15 12:53:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16766.47</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/15 11:12:45</t>
+          <t>10/15 12:50:42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>16766.47</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,166 +1083,181 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1252,7 +1267,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1264,12 +1279,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1279,7 +1294,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1291,12 +1306,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1306,7 +1321,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1318,12 +1333,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1333,7 +1348,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1345,12 +1360,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1360,7 +1375,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1372,12 +1387,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1399,12 +1414,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1414,7 +1429,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1426,12 +1441,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1453,12 +1468,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1468,7 +1483,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1480,12 +1495,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1507,12 +1522,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1534,12 +1549,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1561,12 +1576,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1588,12 +1603,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1615,12 +1630,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1630,7 +1645,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1642,12 +1657,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1657,7 +1672,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1669,12 +1684,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1696,12 +1711,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1723,12 +1738,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1750,12 +1765,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1765,7 +1780,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1777,12 +1792,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1792,7 +1807,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1804,12 +1819,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1831,83 +1846,110 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>4204000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>504651.32</t>
+          <t>4294000</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>492739</t>
+          <t>515116.43</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>492739</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>11912.32</t>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>22377.43</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -1252,12 +1252,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1279,12 +1279,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1306,12 +1306,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1333,12 +1333,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1360,12 +1360,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1414,12 +1414,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1441,12 +1441,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1468,12 +1468,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1495,12 +1495,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1522,12 +1522,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1549,12 +1549,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1576,12 +1576,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1603,12 +1603,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1630,12 +1630,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1684,12 +1684,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1711,12 +1711,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1792,12 +1792,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1819,12 +1819,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1846,12 +1846,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1873,83 +1873,110 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>4294000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>515116.43</t>
+          <t>4294000</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>492739</t>
+          <t>515116.43</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>533204</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>22377.43</t>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>-18087.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -1252,12 +1252,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1279,12 +1279,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1306,12 +1306,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1333,12 +1333,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1360,12 +1360,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1414,12 +1414,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1441,12 +1441,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1468,12 +1468,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1495,12 +1495,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1522,12 +1522,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1549,12 +1549,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1576,12 +1576,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1603,12 +1603,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1630,12 +1630,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1684,12 +1684,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1711,12 +1711,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1792,12 +1792,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1819,12 +1819,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1846,12 +1846,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1900,83 +1900,110 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>4294000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>515116.43</t>
+          <t>4294000</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>533204</t>
+          <t>515116.43</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>543669</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>-18087.57</t>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>-28552.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/18 16:50:27</t>
+          <t>10/19 11:01:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10465.12</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/16 12:34:20</t>
+          <t>10/18 16:50:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>10465.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/15 12:53:40</t>
+          <t>10/16 12:34:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/15 12:50:42</t>
+          <t>10/15 12:53:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16766.47</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/15 11:12:45</t>
+          <t>10/15 12:50:42</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>16766.47</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,166 +1125,181 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1306,12 +1321,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1321,7 +1336,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1333,12 +1348,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1348,7 +1363,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1360,12 +1375,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1375,7 +1390,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1387,12 +1402,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1402,7 +1417,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1414,12 +1429,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1429,7 +1444,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1441,12 +1456,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1456,7 +1471,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1468,12 +1483,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1495,12 +1510,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1510,7 +1525,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1522,12 +1537,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1549,12 +1564,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1564,7 +1579,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1576,12 +1591,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1603,12 +1618,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1630,12 +1645,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1657,12 +1672,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1684,12 +1699,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1711,12 +1726,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1726,7 +1741,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1738,12 +1753,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1753,7 +1768,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1765,12 +1780,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1792,12 +1807,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1819,12 +1834,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1846,12 +1861,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1861,7 +1876,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1873,12 +1888,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1888,7 +1903,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1900,12 +1915,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1927,83 +1942,110 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>4294000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>515116.43</t>
+          <t>4394000</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>543669</t>
+          <t>527237.65</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>543669</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>-28552.57</t>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>-16431.35</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/19 11:01:06</t>
+          <t>10/19 13:54:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/18 16:50:27</t>
+          <t>10/19 11:01:06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10465.12</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/16 12:34:20</t>
+          <t>10/18 16:50:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>10465.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/15 12:53:40</t>
+          <t>10/16 12:34:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/15 12:50:42</t>
+          <t>10/15 12:53:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16766.47</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/15 11:12:45</t>
+          <t>10/15 12:50:42</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>16766.47</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,166 +1167,181 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1348,12 +1363,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1363,7 +1378,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1375,12 +1390,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1390,7 +1405,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1402,12 +1417,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1417,7 +1432,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1429,12 +1444,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1444,7 +1459,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1456,12 +1471,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1471,7 +1486,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1483,12 +1498,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1498,7 +1513,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1510,12 +1525,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1537,12 +1552,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1552,7 +1567,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1564,12 +1579,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1591,12 +1606,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1606,7 +1621,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1618,12 +1633,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1645,12 +1660,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1672,12 +1687,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1699,12 +1714,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1726,12 +1741,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1753,12 +1768,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1768,7 +1783,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1780,12 +1795,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1795,7 +1810,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1807,12 +1822,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1834,12 +1849,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1861,12 +1876,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1888,12 +1903,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1903,7 +1918,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1915,12 +1930,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1930,7 +1945,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1942,12 +1957,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1969,83 +1984,110 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>4394000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>527237.65</t>
+          <t>4524000</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>543669</t>
+          <t>542713.84</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>543669</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>-16431.35</t>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>-955.16</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -1336,12 +1336,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>10/19 15:44:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1363,12 +1363,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1390,12 +1390,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1417,12 +1417,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1444,12 +1444,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1471,12 +1471,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1498,12 +1498,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1552,12 +1552,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1579,12 +1579,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1606,12 +1606,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1660,12 +1660,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1687,12 +1687,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1741,12 +1741,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1768,12 +1768,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1795,12 +1795,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1822,12 +1822,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1849,12 +1849,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1876,12 +1876,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1903,12 +1903,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1930,12 +1930,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1957,12 +1957,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1984,12 +1984,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2011,83 +2011,110 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>4524000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>542713.84</t>
+          <t>4524000</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>543669</t>
+          <t>542713.84</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>571266</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>-955.16</t>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>-28552.16</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/19 13:54:56</t>
+          <t>10/20 13:42:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>19393.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/19 11:01:06</t>
+          <t>10/19 13:54:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/18 16:50:27</t>
+          <t>10/19 11:01:06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10465.12</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/16 12:34:20</t>
+          <t>10/18 16:50:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>10465.12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/15 12:53:40</t>
+          <t>10/16 12:34:20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/15 12:50:42</t>
+          <t>10/15 12:53:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16766.47</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/15 11:12:45</t>
+          <t>10/15 12:50:42</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>16766.47</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,166 +1209,181 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/19 15:44:08</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>10/19 15:44:08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1390,12 +1405,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1417,12 +1432,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1432,7 +1447,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1444,12 +1459,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1459,7 +1474,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1471,12 +1486,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1486,7 +1501,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1498,12 +1513,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1513,7 +1528,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1525,12 +1540,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1540,7 +1555,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1552,12 +1567,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1567,7 +1582,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1579,12 +1594,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1606,12 +1621,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1621,7 +1636,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1633,12 +1648,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1660,12 +1675,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1675,7 +1690,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1687,12 +1702,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1714,12 +1729,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1741,12 +1756,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1768,12 +1783,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1795,12 +1810,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1822,12 +1837,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1837,7 +1852,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1849,12 +1864,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1864,7 +1879,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1876,12 +1891,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1903,12 +1918,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1930,12 +1945,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1957,12 +1972,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1972,7 +1987,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1984,12 +1999,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1999,7 +2014,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2011,12 +2026,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2038,83 +2053,110 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>4524000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>542713.84</t>
+          <t>4684000</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>571266</t>
+          <t>562107.78</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>571266</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>-28552.16</t>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>-9158.22</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -1378,12 +1378,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/19 15:44:08</t>
+          <t>10/20 16:00:52</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1405,12 +1405,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>10/19 15:44:08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1486,12 +1486,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1513,12 +1513,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1540,12 +1540,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1594,12 +1594,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1621,12 +1621,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1648,12 +1648,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1702,12 +1702,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1729,12 +1729,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1756,12 +1756,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1783,12 +1783,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1810,12 +1810,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1837,12 +1837,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1864,12 +1864,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1891,12 +1891,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1918,12 +1918,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1972,12 +1972,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1999,12 +1999,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2026,12 +2026,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2053,12 +2053,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2080,83 +2080,110 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>4684000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>562107.78</t>
+          <t>4684000</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>571266</t>
+          <t>562107.78</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>590659</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>-9158.22</t>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>-28551.22</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/20 13:42:09</t>
+          <t>10/21 11:09:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19393.94</t>
+          <t>16626.51</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/19 13:54:56</t>
+          <t>10/20 13:42:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>19393.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/19 11:01:06</t>
+          <t>10/19 13:54:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/18 16:50:27</t>
+          <t>10/19 11:01:06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10465.12</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/16 12:34:20</t>
+          <t>10/18 16:50:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>10465.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/15 12:53:40</t>
+          <t>10/16 12:34:20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/15 12:50:42</t>
+          <t>10/15 12:53:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16766.47</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/15 11:12:45</t>
+          <t>10/15 12:50:42</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>16766.47</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,7 +1167,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,166 +1251,181 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/20 16:00:52</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/19 15:44:08</t>
+          <t>10/20 16:00:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1420,7 +1435,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1432,12 +1447,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>10/19 15:44:08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1459,12 +1474,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1486,12 +1501,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1501,7 +1516,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1513,12 +1528,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1528,7 +1543,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1540,12 +1555,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1555,7 +1570,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1567,12 +1582,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1582,7 +1597,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1594,12 +1609,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1609,7 +1624,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1621,12 +1636,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1636,7 +1651,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1648,12 +1663,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1675,12 +1690,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1690,7 +1705,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1702,12 +1717,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1729,12 +1744,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1744,7 +1759,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1756,12 +1771,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1783,12 +1798,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1810,12 +1825,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1837,12 +1852,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1864,12 +1879,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1891,12 +1906,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1906,7 +1921,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1918,12 +1933,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1933,7 +1948,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1945,12 +1960,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1972,12 +1987,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1999,12 +2014,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2026,12 +2041,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2041,7 +2056,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2053,12 +2068,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2068,7 +2083,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2080,12 +2095,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2107,83 +2122,110 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>4684000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>562107.78</t>
+          <t>4822000</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>590659</t>
+          <t>578734.28</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>590659</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>-28551.22</t>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>-11924.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -1420,12 +1420,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/20 16:00:52</t>
+          <t>10/21 13:39:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1447,12 +1447,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/19 15:44:08</t>
+          <t>10/20 16:00:52</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1474,12 +1474,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>10/19 15:44:08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1528,12 +1528,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1555,12 +1555,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1582,12 +1582,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1636,12 +1636,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1663,12 +1663,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1690,12 +1690,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1717,12 +1717,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1744,12 +1744,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1771,12 +1771,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1798,12 +1798,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1825,12 +1825,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1852,12 +1852,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1879,12 +1879,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1906,12 +1906,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1933,12 +1933,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1960,12 +1960,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1987,12 +1987,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2014,12 +2014,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2041,12 +2041,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2068,12 +2068,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2122,12 +2122,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2149,83 +2149,110 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="69"/>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>4822000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>578734.28</t>
+          <t>4822000</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>590659</t>
+          <t>578734.28</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>607285</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>-11924.72</t>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>-28550.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/21 11:09:11</t>
+          <t>10/26 10:32:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>129840</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16626.51</t>
+          <t>15457.14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/20 13:42:09</t>
+          <t>10/21 11:09:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19393.94</t>
+          <t>16626.51</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/19 13:54:56</t>
+          <t>10/20 13:42:09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>19393.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/19 11:01:06</t>
+          <t>10/19 13:54:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/18 16:50:27</t>
+          <t>10/19 11:01:06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10465.12</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/16 12:34:20</t>
+          <t>10/18 16:50:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>10465.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/15 12:53:40</t>
+          <t>10/16 12:34:20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/15 12:50:42</t>
+          <t>10/15 12:53:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16766.47</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/15 11:12:45</t>
+          <t>10/15 12:50:42</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>16766.47</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,166 +1293,181 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/21 13:39:36</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/20 16:00:52</t>
+          <t>10/21 13:39:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1462,7 +1477,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1474,12 +1489,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/19 15:44:08</t>
+          <t>10/20 16:00:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1489,7 +1504,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1501,12 +1516,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>10/19 15:44:08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1528,12 +1543,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1555,12 +1570,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1570,7 +1585,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1582,12 +1597,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1597,7 +1612,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1609,12 +1624,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1624,7 +1639,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1636,12 +1651,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1651,7 +1666,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1663,12 +1678,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1678,7 +1693,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1690,12 +1705,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1705,7 +1720,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1717,12 +1732,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1744,12 +1759,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1759,7 +1774,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1771,12 +1786,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1798,12 +1813,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1813,7 +1828,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1825,12 +1840,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1852,12 +1867,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1879,12 +1894,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1906,12 +1921,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1933,12 +1948,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1960,12 +1975,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1975,7 +1990,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1987,12 +2002,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2002,7 +2017,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2014,12 +2029,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2041,12 +2056,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2068,12 +2083,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2095,12 +2110,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2110,7 +2125,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2122,12 +2137,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2137,7 +2152,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2149,12 +2164,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2176,83 +2191,110 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>4822000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>578734.28</t>
+          <t>4951840</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>607285</t>
+          <t>594191.43</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>607285</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>-28550.72</t>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>-13093.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 10:32:43</t>
+          <t>10/26 11:41:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>129840</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15457.14</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/21 11:09:11</t>
+          <t>10/26 10:32:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>129840</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16626.51</t>
+          <t>15457.14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/20 13:42:09</t>
+          <t>10/21 11:09:11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19393.94</t>
+          <t>16626.51</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/19 13:54:56</t>
+          <t>10/20 13:42:09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>19393.94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/19 11:01:06</t>
+          <t>10/19 13:54:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/18 16:50:27</t>
+          <t>10/19 11:01:06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10465.12</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/16 12:34:20</t>
+          <t>10/18 16:50:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>10465.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/15 12:53:40</t>
+          <t>10/16 12:34:20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/15 12:50:42</t>
+          <t>10/15 12:53:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16766.47</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/15 11:12:45</t>
+          <t>10/15 12:50:42</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>16766.47</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,7 +957,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,166 +1335,181 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/21 13:39:36</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/20 16:00:52</t>
+          <t>10/21 13:39:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1504,7 +1519,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1516,12 +1531,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/19 15:44:08</t>
+          <t>10/20 16:00:52</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1531,7 +1546,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1543,12 +1558,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>10/19 15:44:08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1570,12 +1585,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1597,12 +1612,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1612,7 +1627,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1624,12 +1639,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1639,7 +1654,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1651,12 +1666,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1666,7 +1681,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1678,12 +1693,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1693,7 +1708,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1705,12 +1720,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1720,7 +1735,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1732,12 +1747,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1747,7 +1762,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1759,12 +1774,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1786,12 +1801,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1801,7 +1816,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1813,12 +1828,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1840,12 +1855,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1855,7 +1870,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1867,12 +1882,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1894,12 +1909,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1921,12 +1936,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1948,12 +1963,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1975,12 +1990,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2002,12 +2017,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2017,7 +2032,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2029,12 +2044,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2044,7 +2059,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2056,12 +2071,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2083,12 +2098,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2110,12 +2125,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2137,12 +2152,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2152,7 +2167,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2164,12 +2179,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2179,7 +2194,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2191,12 +2206,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2218,83 +2233,110 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>4951840</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>594191.43</t>
+          <t>5251840</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>607285</t>
+          <t>630336</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>607285</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>-13093.57</t>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>23051</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 11:41:16</t>
+          <t>10/26 13:26:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>128316</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>15275.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/26 10:32:43</t>
+          <t>10/26 11:41:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>129840</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15457.14</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/21 11:09:11</t>
+          <t>10/26 10:32:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>129840</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16626.51</t>
+          <t>15457.14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/20 13:42:09</t>
+          <t>10/21 11:09:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19393.94</t>
+          <t>16626.51</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/19 13:54:56</t>
+          <t>10/20 13:42:09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>19393.94</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/19 11:01:06</t>
+          <t>10/19 13:54:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/18 16:50:27</t>
+          <t>10/19 11:01:06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10465.12</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/16 12:34:20</t>
+          <t>10/18 16:50:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>10465.12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/15 12:53:40</t>
+          <t>10/16 12:34:20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/15 12:50:42</t>
+          <t>10/15 12:53:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16766.47</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/15 11:12:45</t>
+          <t>10/15 12:50:42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>16766.47</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,7 +1293,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1377,166 +1377,181 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/21 13:39:36</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/20 16:00:52</t>
+          <t>10/21 13:39:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1546,7 +1561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1558,12 +1573,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/19 15:44:08</t>
+          <t>10/20 16:00:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1573,7 +1588,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1585,12 +1600,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>10/19 15:44:08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1612,12 +1627,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1639,12 +1654,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1654,7 +1669,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1666,12 +1681,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1681,7 +1696,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1693,12 +1708,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1708,7 +1723,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1720,12 +1735,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1735,7 +1750,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1747,12 +1762,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1762,7 +1777,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1774,12 +1789,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1789,7 +1804,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1801,12 +1816,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1828,12 +1843,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1843,7 +1858,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1855,12 +1870,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1882,12 +1897,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1897,7 +1912,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1909,12 +1924,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1936,12 +1951,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1963,12 +1978,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1990,12 +2005,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2017,12 +2032,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2044,12 +2059,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2059,7 +2074,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2071,12 +2086,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2086,7 +2101,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2098,12 +2113,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2125,12 +2140,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2152,12 +2167,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2179,12 +2194,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2194,7 +2209,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2206,12 +2221,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2221,7 +2236,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2233,12 +2248,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2260,83 +2275,110 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>5251840</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>630336</t>
+          <t>5380156</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>607285</t>
+          <t>645611.72</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>607285</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>23051</t>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>38326.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -1546,12 +1546,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/21 13:39:36</t>
+          <t>10/26 13:29:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>51420</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1573,12 +1573,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/20 16:00:52</t>
+          <t>10/21 13:39:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1600,12 +1600,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/19 15:44:08</t>
+          <t>10/20 16:00:52</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>10/19 15:44:08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1708,12 +1708,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1735,12 +1735,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1762,12 +1762,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1789,12 +1789,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1816,12 +1816,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1843,12 +1843,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1870,12 +1870,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1897,12 +1897,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1924,12 +1924,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1951,12 +1951,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1978,12 +1978,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2005,12 +2005,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2032,12 +2032,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2086,12 +2086,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2140,12 +2140,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2167,12 +2167,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2194,12 +2194,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2221,12 +2221,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2248,12 +2248,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2275,12 +2275,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2302,83 +2302,110 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="73"/>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>5380156</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>645611.72</t>
+          <t>5380156</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>607285</t>
+          <t>645611.72</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>658705</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>38326.72</t>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>-13093.28</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 13:26:45</t>
+          <t>10/28 13:18:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>128316</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15275.71</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/26 11:41:16</t>
+          <t>10/26 13:26:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>128316</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>15275.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/26 10:32:43</t>
+          <t>10/26 11:41:16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129840</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15457.14</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/21 11:09:11</t>
+          <t>10/26 10:32:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>129840</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16626.51</t>
+          <t>15457.14</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/20 13:42:09</t>
+          <t>10/21 11:09:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19393.94</t>
+          <t>16626.51</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/19 13:54:56</t>
+          <t>10/20 13:42:09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>19393.94</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/19 11:01:06</t>
+          <t>10/19 13:54:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/18 16:50:27</t>
+          <t>10/19 11:01:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10465.12</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/16 12:34:20</t>
+          <t>10/18 16:50:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>10465.12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/15 12:53:40</t>
+          <t>10/16 12:34:20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/15 12:50:42</t>
+          <t>10/15 12:53:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16766.47</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/15 11:12:45</t>
+          <t>10/15 12:50:42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>16766.47</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/06 10:20:11</t>
+          <t>10/06 12:40:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>9411.76</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/23 12:37:12</t>
+          <t>09/23 13:35:49</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/23 12:36:02</t>
+          <t>09/23 12:37:12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/19 14:13:44</t>
+          <t>09/14 10:06:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/13 12:08:49</t>
+          <t>07/13 13:37:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>60975.61</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1419,166 +1419,181 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>07/13 12:08:49</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>20833.33</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>07/08 11:28:20</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>23529.41</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/26 13:29:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>51420</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/21 13:39:36</t>
+          <t>10/26 13:29:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>51420</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1600,12 +1615,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/20 16:00:52</t>
+          <t>10/21 13:39:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1615,7 +1630,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1627,12 +1642,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10/19 15:44:08</t>
+          <t>10/20 16:00:52</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1642,7 +1657,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1654,12 +1669,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>10/19 15:44:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1681,12 +1696,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1708,12 +1723,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1723,7 +1738,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1735,12 +1750,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1750,7 +1765,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1762,12 +1777,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1777,7 +1792,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1789,12 +1804,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1804,7 +1819,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1816,12 +1831,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1831,7 +1846,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1843,12 +1858,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1858,7 +1873,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1870,12 +1885,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1897,12 +1912,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1912,7 +1927,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1924,12 +1939,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1951,12 +1966,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1966,7 +1981,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1978,12 +1993,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2005,12 +2020,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2032,12 +2047,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2059,12 +2074,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2086,12 +2101,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2113,12 +2128,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2128,7 +2143,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2140,12 +2155,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2155,7 +2170,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2167,12 +2182,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2194,12 +2209,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2221,12 +2236,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2248,12 +2263,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2263,7 +2278,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2275,12 +2290,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2290,7 +2305,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2302,12 +2317,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2329,83 +2344,110 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>5380156</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>645611.72</t>
+          <t>5510156</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>658705</t>
+          <t>661087.91</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>658705</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>-13093.28</t>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2382.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-all.xlsx
@@ -1588,12 +1588,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/26 13:29:32</t>
+          <t>10/28 15:01:09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>51420</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1615,12 +1615,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/21 13:39:36</t>
+          <t>10/26 13:29:32</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>51420</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1642,12 +1642,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10/20 16:00:52</t>
+          <t>10/21 13:39:36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1669,12 +1669,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10/19 15:44:08</t>
+          <t>10/20 16:00:52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1696,12 +1696,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10/18 18:07:35</t>
+          <t>10/19 15:44:08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1750,12 +1750,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10/16 13:57:19</t>
+          <t>10/18 18:07:10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1777,12 +1777,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10/15 14:16:29</t>
+          <t>10/16 13:57:19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1804,12 +1804,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10/12 14:42:22</t>
+          <t>10/15 14:16:29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
+          <t>10/12 14:42:22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1858,12 +1858,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>10/06 15:03:42</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1885,12 +1885,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/30 11:43:33</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1912,12 +1912,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/29 13:06:13</t>
+          <t>09/30 11:43:33</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1939,12 +1939,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1966,12 +1966,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/27 12:36:22</t>
+          <t>09/28 18:19:39</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1993,12 +1993,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/25 15:00:33</t>
+          <t>09/27 12:36:22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2020,12 +2020,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
+          <t>09/25 15:00:33</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2047,12 +2047,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/22 20:12:06</t>
+          <t>09/23 14:50:17</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2074,12 +2074,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2101,12 +2101,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>09/22 19:12:35</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2128,12 +2128,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/21 15:47:11</t>
+          <t>09/22 19:11:34</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
+          <t>09/21 15:47:11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2182,12 +2182,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/18 14:31:58</t>
+          <t>09/21 14:18:50</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/17 11:35:17</t>
+          <t>09/18 14:31:58</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2236,12 +2236,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09/14 11:52:43</t>
+          <t>09/17 11:35:17</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2263,12 +2263,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08/19 15:39:23</t>
+          <t>09/14 11:52:43</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2290,12 +2290,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/15 20:32:10</t>
+          <t>08/19 15:39:23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2317,12 +2317,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
+          <t>07/15 20:32:10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2344,12 +2344,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/08 14:14:50</t>
+          <t>07/13 15:24:33</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2371,83 +2371,110 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>5510156</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>661087.91</t>
+          <t>5510156</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>658705</t>
+          <t>661087.91</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>674181</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2382.91</t>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>-13093.09</t>
         </is>
       </c>
     </row>
